--- a/data/trans_orig/P6710-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P6710-Estudios-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si puede decidir cuándo hace un descanso en 2012</t>
+          <t>Población según si puede decidir cuándo hace un descanso en 2012 (tasa de respuesta: 98,74%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10907</t>
+          <t>10322</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28202</t>
+          <t>27067</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11866</t>
+          <t>11665</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>29096</t>
+          <t>27172</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>25593</t>
+          <t>25282</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>49151</t>
+          <t>48448</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,16%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5533</t>
+          <t>5484</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20035</t>
+          <t>19409</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4321</t>
+          <t>4115</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16697</t>
+          <t>16913</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>12996</t>
+          <t>12889</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>31426</t>
+          <t>30595</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,57%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>19317</t>
+          <t>18904</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>40436</t>
+          <t>40525</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>12373</t>
+          <t>11657</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>29514</t>
+          <t>28755</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>35864</t>
+          <t>35663</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>62665</t>
+          <t>64715</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>20,25%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24711</t>
+          <t>25248</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>46552</t>
+          <t>45425</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11244</t>
+          <t>11033</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28553</t>
+          <t>27537</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>40222</t>
+          <t>39869</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>67808</t>
+          <t>67363</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>21,08%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>75976</t>
+          <t>77053</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>103432</t>
+          <t>104326</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>41,84%</t>
+          <t>42,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>56,96%</t>
+          <t>57,45%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>59469</t>
+          <t>61034</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>85196</t>
+          <t>85535</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>43,1%</t>
+          <t>44,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>61,74%</t>
+          <t>61,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>143213</t>
+          <t>145013</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>180216</t>
+          <t>181549</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>44,81%</t>
+          <t>45,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>56,39%</t>
+          <t>56,81%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>78422</t>
+          <t>81181</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>119503</t>
+          <t>119096</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>57012</t>
+          <t>56564</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>90469</t>
+          <t>89175</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>145077</t>
+          <t>145750</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>195585</t>
+          <t>198045</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,39%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>60556</t>
+          <t>59455</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>95788</t>
+          <t>96562</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>50214</t>
+          <t>48315</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>81212</t>
+          <t>79786</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>118594</t>
+          <t>118018</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>164724</t>
+          <t>168992</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,42%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>171288</t>
+          <t>172113</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>220770</t>
+          <t>223032</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>89800</t>
+          <t>91043</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>128973</t>
+          <t>127777</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>273203</t>
+          <t>272025</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>336071</t>
+          <t>334384</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>22,6%</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>172588</t>
+          <t>171403</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>223200</t>
+          <t>219577</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>109991</t>
+          <t>111498</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>148812</t>
+          <t>150519</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>26,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>292109</t>
+          <t>293820</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>359323</t>
+          <t>361829</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,46%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>315530</t>
+          <t>313122</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>375527</t>
+          <t>373655</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>34,68%</t>
+          <t>34,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>41,27%</t>
+          <t>41,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>173738</t>
+          <t>174752</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>221037</t>
+          <t>221943</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>30,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>38,8%</t>
+          <t>38,96%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>498918</t>
+          <t>500869</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>578342</t>
+          <t>578834</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>33,72%</t>
+          <t>33,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>39,09%</t>
+          <t>39,12%</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>15529</t>
+          <t>15016</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>34652</t>
+          <t>33535</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>22850</t>
+          <t>22544</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>45596</t>
+          <t>44855</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2145,12 +2145,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>42063</t>
+          <t>41830</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>71303</t>
+          <t>72044</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>13,19%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15104</t>
+          <t>15768</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>36869</t>
+          <t>37153</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11612</t>
+          <t>10862</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>31185</t>
+          <t>29984</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>29898</t>
+          <t>30287</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>58137</t>
+          <t>58662</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,74%</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>55025</t>
+          <t>54027</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>86964</t>
+          <t>83549</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>36743</t>
+          <t>37302</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>62699</t>
+          <t>65171</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>97773</t>
+          <t>100496</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>140152</t>
+          <t>142623</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>26,11%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>55296</t>
+          <t>54436</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>84795</t>
+          <t>87277</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>27,76%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>28706</t>
+          <t>27531</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>51040</t>
+          <t>51722</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>22,3%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>89091</t>
+          <t>88302</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>127687</t>
+          <t>127319</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,31%</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>111230</t>
+          <t>110586</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>148179</t>
+          <t>146523</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>35,38%</t>
+          <t>35,18%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>47,14%</t>
+          <t>46,61%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>75656</t>
+          <t>75452</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>108816</t>
+          <t>107408</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>32,62%</t>
+          <t>32,53%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>46,91%</t>
+          <t>46,31%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>195709</t>
+          <t>194132</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>244661</t>
+          <t>243662</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>35,54%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>44,79%</t>
+          <t>44,6%</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>114041</t>
+          <t>118233</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>162634</t>
+          <t>165384</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>102582</t>
+          <t>103459</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>146832</t>
+          <t>146748</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>229849</t>
+          <t>230920</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>294059</t>
+          <t>294422</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,55%</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>91514</t>
+          <t>94489</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>134739</t>
+          <t>135014</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,12 +2905,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>73172</t>
+          <t>73546</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>112272</t>
+          <t>112710</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>176290</t>
+          <t>177045</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>231647</t>
+          <t>234608</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2975,12 +2975,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>10,0%</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>263169</t>
+          <t>262690</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>324470</t>
+          <t>324861</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>152255</t>
+          <t>152289</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>202301</t>
+          <t>203321</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>430279</t>
+          <t>428570</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>511194</t>
+          <t>510312</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>21,76%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>267847</t>
+          <t>268847</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>332086</t>
+          <t>336195</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>164138</t>
+          <t>163306</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>214684</t>
+          <t>211894</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>449024</t>
+          <t>444852</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>527836</t>
+          <t>525678</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,41%</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>524110</t>
+          <t>521038</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>603506</t>
+          <t>596518</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>37,06%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>42,93%</t>
+          <t>42,43%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>331193</t>
+          <t>329605</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>391106</t>
+          <t>392114</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>35,25%</t>
+          <t>35,08%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>41,63%</t>
+          <t>41,73%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>874574</t>
+          <t>873818</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>974065</t>
+          <t>967892</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>37,29%</t>
+          <t>37,26%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>41,53%</t>
+          <t>41,27%</t>
         </is>
       </c>
     </row>
@@ -3495,7 +3495,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si puede decidir cuándo hace un descanso en 2016</t>
+          <t>Población según si puede decidir cuándo hace un descanso en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3690,12 +3690,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15023</t>
+          <t>15303</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>32792</t>
+          <t>33044</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3705,12 +3705,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8861</t>
+          <t>8934</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22444</t>
+          <t>21767</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3740,12 +3740,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>30,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>27788</t>
+          <t>27946</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>51041</t>
+          <t>49641</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3775,12 +3775,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,07%</t>
         </is>
       </c>
     </row>
@@ -3803,12 +3803,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12024</t>
+          <t>12903</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>31074</t>
+          <t>32365</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3818,12 +3818,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4328</t>
+          <t>4785</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16356</t>
+          <t>15999</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3853,12 +3853,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>20558</t>
+          <t>20619</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>41591</t>
+          <t>41388</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>19,23%</t>
         </is>
       </c>
     </row>
@@ -3916,12 +3916,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>21201</t>
+          <t>20814</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>40697</t>
+          <t>40422</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3931,12 +3931,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>28,24%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3951,12 +3951,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>11698</t>
+          <t>11437</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>25851</t>
+          <t>25729</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3966,12 +3966,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>35,86%</t>
+          <t>35,69%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3986,12 +3986,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>34862</t>
+          <t>35387</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>60397</t>
+          <t>59948</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>27,86%</t>
         </is>
       </c>
     </row>
@@ -4029,12 +4029,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>26255</t>
+          <t>26847</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>48562</t>
+          <t>47719</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4044,12 +4044,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,93%</t>
+          <t>33,34%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4064,12 +4064,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13203</t>
+          <t>12930</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28059</t>
+          <t>27796</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4079,12 +4079,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,92%</t>
+          <t>38,56%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4099,12 +4099,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>44386</t>
+          <t>43299</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>70137</t>
+          <t>70295</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4114,12 +4114,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,59%</t>
+          <t>32,66%</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>24102</t>
+          <t>23669</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>44711</t>
+          <t>44243</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>30,91%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>5522</t>
+          <t>5186</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>17765</t>
+          <t>17204</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>32606</t>
+          <t>32826</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>57048</t>
+          <t>55923</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>25,99%</t>
         </is>
       </c>
     </row>
@@ -4372,12 +4372,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>92273</t>
+          <t>91618</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>135226</t>
+          <t>133472</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4387,12 +4387,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4407,12 +4407,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>73593</t>
+          <t>74549</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>108764</t>
+          <t>110078</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4422,12 +4422,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>176407</t>
+          <t>177983</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>231139</t>
+          <t>234373</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4457,12 +4457,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,85%</t>
         </is>
       </c>
     </row>
@@ -4485,12 +4485,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>133911</t>
+          <t>133598</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>180693</t>
+          <t>178112</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4500,12 +4500,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4520,12 +4520,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>108572</t>
+          <t>108449</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>148761</t>
+          <t>148540</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4535,12 +4535,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4555,12 +4555,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>253773</t>
+          <t>254956</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>313488</t>
+          <t>314743</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>19,95%</t>
         </is>
       </c>
     </row>
@@ -4598,12 +4598,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>215286</t>
+          <t>216398</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>273545</t>
+          <t>272556</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4613,12 +4613,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,39%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4633,12 +4633,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>148676</t>
+          <t>148002</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>193116</t>
+          <t>193259</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>29,61%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>379787</t>
+          <t>377362</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>450881</t>
+          <t>450181</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>28,53%</t>
         </is>
       </c>
     </row>
@@ -4711,12 +4711,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>173978</t>
+          <t>172228</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>223899</t>
+          <t>222894</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4726,12 +4726,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4746,12 +4746,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>110243</t>
+          <t>110601</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>148413</t>
+          <t>151737</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4781,12 +4781,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>293959</t>
+          <t>294816</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>358682</t>
+          <t>359319</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>22,77%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>186831</t>
+          <t>190453</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>240495</t>
+          <t>242031</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>115253</t>
+          <t>117161</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>157442</t>
+          <t>159712</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>320445</t>
+          <t>320138</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>386873</t>
+          <t>385829</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>24,45%</t>
         </is>
       </c>
     </row>
@@ -5054,12 +5054,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>33666</t>
+          <t>34019</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>61365</t>
+          <t>59800</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5069,12 +5069,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5089,12 +5089,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>38132</t>
+          <t>38500</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>64128</t>
+          <t>64142</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5104,7 +5104,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -5124,12 +5124,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>77428</t>
+          <t>77599</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>113914</t>
+          <t>114453</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>17,37%</t>
         </is>
       </c>
     </row>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>36668</t>
+          <t>35915</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>64388</t>
+          <t>62921</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5182,12 +5182,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5202,12 +5202,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>40314</t>
+          <t>40097</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>66931</t>
+          <t>66611</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5237,12 +5237,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>84417</t>
+          <t>81579</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>119745</t>
+          <t>120765</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>18,32%</t>
         </is>
       </c>
     </row>
@@ -5280,12 +5280,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>73269</t>
+          <t>73192</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>105464</t>
+          <t>107189</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5295,12 +5295,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>30,57%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5315,12 +5315,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>60482</t>
+          <t>60842</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>90242</t>
+          <t>90132</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,72%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>29,22%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5350,12 +5350,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>142607</t>
+          <t>142940</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>185754</t>
+          <t>189019</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5365,12 +5365,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>28,68%</t>
         </is>
       </c>
     </row>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>49551</t>
+          <t>48985</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>79451</t>
+          <t>80191</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5408,12 +5408,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5428,12 +5428,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>30740</t>
+          <t>30408</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>53058</t>
+          <t>53888</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>87326</t>
+          <t>86210</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>126412</t>
+          <t>126609</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>19,21%</t>
         </is>
       </c>
     </row>
@@ -5506,12 +5506,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>86348</t>
+          <t>86354</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>121898</t>
+          <t>120910</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>34,77%</t>
+          <t>34,49%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>73225</t>
+          <t>74673</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>106557</t>
+          <t>106721</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>34,55%</t>
+          <t>34,6%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>171000</t>
+          <t>170465</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>220392</t>
+          <t>217718</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>33,44%</t>
+          <t>33,03%</t>
         </is>
       </c>
     </row>
@@ -5736,12 +5736,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>154058</t>
+          <t>156841</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>209073</t>
+          <t>207350</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5751,12 +5751,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5771,12 +5771,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>134284</t>
+          <t>135195</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>181275</t>
+          <t>181116</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>302556</t>
+          <t>303396</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>373220</t>
+          <t>373921</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,25%</t>
         </is>
       </c>
     </row>
@@ -5849,12 +5849,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>197256</t>
+          <t>196837</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>251842</t>
+          <t>253026</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5864,12 +5864,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5884,12 +5884,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>164899</t>
+          <t>164684</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>215453</t>
+          <t>216219</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>376172</t>
+          <t>374730</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>451828</t>
+          <t>449772</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>18,34%</t>
         </is>
       </c>
     </row>
@@ -5962,12 +5962,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>329977</t>
+          <t>329071</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>399326</t>
+          <t>395486</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5977,12 +5977,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>23,19%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>27,87%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5997,12 +5997,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>232933</t>
+          <t>236126</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>291468</t>
+          <t>290636</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6012,12 +6012,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>28,13%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6032,12 +6032,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>584745</t>
+          <t>580631</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>671034</t>
+          <t>668792</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6047,12 +6047,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>27,27%</t>
         </is>
       </c>
     </row>
@@ -6075,12 +6075,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>268709</t>
+          <t>268488</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>333803</t>
+          <t>329547</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6090,12 +6090,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6110,12 +6110,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>164753</t>
+          <t>168092</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>216982</t>
+          <t>215947</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6125,12 +6125,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>445040</t>
+          <t>449026</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>528157</t>
+          <t>530055</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6160,12 +6160,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>21,62%</t>
         </is>
       </c>
     </row>
@@ -6188,12 +6188,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>320753</t>
+          <t>322563</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>384117</t>
+          <t>386359</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6203,12 +6203,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6223,12 +6223,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>209343</t>
+          <t>207760</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>264266</t>
+          <t>264228</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6238,7 +6238,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>546956</t>
+          <t>544049</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>631167</t>
+          <t>633436</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6273,12 +6273,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>25,83%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P6710-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P6710-Estudios-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10322</t>
+          <t>10370</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27067</t>
+          <t>27742</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11665</t>
+          <t>11568</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27172</t>
+          <t>27712</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>25282</t>
+          <t>26301</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>48448</t>
+          <t>50501</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,8%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5484</t>
+          <t>5798</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19409</t>
+          <t>19646</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4115</t>
+          <t>4195</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16913</t>
+          <t>16530</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>12889</t>
+          <t>12608</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>30595</t>
+          <t>30602</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,58%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>18904</t>
+          <t>19732</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>40525</t>
+          <t>40670</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>11657</t>
+          <t>11180</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>28755</t>
+          <t>27622</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>35663</t>
+          <t>35914</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>64715</t>
+          <t>63043</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>19,73%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25248</t>
+          <t>25323</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>45425</t>
+          <t>46162</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11033</t>
+          <t>11248</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27537</t>
+          <t>28048</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>39869</t>
+          <t>39986</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>67363</t>
+          <t>66210</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>20,72%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>77053</t>
+          <t>75896</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>104326</t>
+          <t>102874</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>42,43%</t>
+          <t>41,79%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>57,45%</t>
+          <t>56,65%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>61034</t>
+          <t>60197</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>85535</t>
+          <t>84184</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>44,23%</t>
+          <t>43,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>61,99%</t>
+          <t>61,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>145013</t>
+          <t>143954</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>181549</t>
+          <t>178902</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>45,37%</t>
+          <t>45,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>56,81%</t>
+          <t>55,98%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>81181</t>
+          <t>79590</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>119096</t>
+          <t>118383</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>56564</t>
+          <t>57327</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>89175</t>
+          <t>89997</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>145750</t>
+          <t>145456</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>198045</t>
+          <t>194265</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,13%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>59455</t>
+          <t>59677</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>96562</t>
+          <t>95555</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>48315</t>
+          <t>48480</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>79786</t>
+          <t>82103</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>118018</t>
+          <t>116505</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>168992</t>
+          <t>162304</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>10,97%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>172113</t>
+          <t>172615</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>223032</t>
+          <t>223796</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>91043</t>
+          <t>90229</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>127777</t>
+          <t>129328</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>272025</t>
+          <t>272841</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>334384</t>
+          <t>336853</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>22,77%</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>171403</t>
+          <t>170569</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>219577</t>
+          <t>221161</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>111498</t>
+          <t>110155</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>150519</t>
+          <t>149713</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>26,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>293820</t>
+          <t>293876</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>361829</t>
+          <t>363516</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,7 +1842,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>24,57%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>313122</t>
+          <t>314473</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>373655</t>
+          <t>374057</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>34,42%</t>
+          <t>34,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>41,07%</t>
+          <t>41,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>174752</t>
+          <t>175923</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>221943</t>
+          <t>222175</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>30,68%</t>
+          <t>30,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>38,96%</t>
+          <t>39,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>500869</t>
+          <t>504391</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>578834</t>
+          <t>579767</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>34,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>39,12%</t>
+          <t>39,19%</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>15016</t>
+          <t>15065</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>33535</t>
+          <t>33092</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>22544</t>
+          <t>22256</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>44855</t>
+          <t>45974</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2145,12 +2145,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>41830</t>
+          <t>41513</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>72044</t>
+          <t>71563</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,1%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15768</t>
+          <t>15445</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>37153</t>
+          <t>36481</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10862</t>
+          <t>11219</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>29984</t>
+          <t>29627</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>30287</t>
+          <t>30547</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>58662</t>
+          <t>56859</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,41%</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>54027</t>
+          <t>54710</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>83549</t>
+          <t>85170</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>27,09%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>37302</t>
+          <t>38227</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>65171</t>
+          <t>64927</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>27,99%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>100496</t>
+          <t>100409</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>142623</t>
+          <t>142121</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>26,02%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>54436</t>
+          <t>54840</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>87277</t>
+          <t>86374</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>27,48%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>27531</t>
+          <t>27969</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>51722</t>
+          <t>51763</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>88302</t>
+          <t>88765</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>127319</t>
+          <t>128739</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>23,57%</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>110586</t>
+          <t>110729</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>146523</t>
+          <t>145986</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>35,22%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>46,61%</t>
+          <t>46,44%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>75452</t>
+          <t>76818</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>107408</t>
+          <t>109139</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>46,31%</t>
+          <t>47,05%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>194132</t>
+          <t>194787</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>243662</t>
+          <t>246094</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>35,54%</t>
+          <t>35,66%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>44,6%</t>
+          <t>45,05%</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>118233</t>
+          <t>114867</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>165384</t>
+          <t>162680</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>103459</t>
+          <t>102717</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>146748</t>
+          <t>146562</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>230920</t>
+          <t>230868</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>294422</t>
+          <t>293295</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,51%</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>94489</t>
+          <t>92300</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>135014</t>
+          <t>132778</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,12 +2905,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>73546</t>
+          <t>71169</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>112710</t>
+          <t>110619</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>177045</t>
+          <t>175101</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>234608</t>
+          <t>237068</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2975,12 +2975,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,11%</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>262690</t>
+          <t>262970</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>324861</t>
+          <t>323636</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>152289</t>
+          <t>153889</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>203321</t>
+          <t>203935</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>428570</t>
+          <t>428918</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>510312</t>
+          <t>510691</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>21,77%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>268847</t>
+          <t>268143</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>336195</t>
+          <t>330594</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>163306</t>
+          <t>163132</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>211894</t>
+          <t>214357</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>444852</t>
+          <t>447200</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>525678</t>
+          <t>526247</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,44%</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>521038</t>
+          <t>522005</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>596518</t>
+          <t>603887</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>37,06%</t>
+          <t>37,13%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>42,43%</t>
+          <t>42,96%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>329605</t>
+          <t>332532</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>392114</t>
+          <t>391104</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>35,39%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>41,73%</t>
+          <t>41,63%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>873818</t>
+          <t>879100</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>967892</t>
+          <t>973043</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>37,26%</t>
+          <t>37,48%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>41,27%</t>
+          <t>41,49%</t>
         </is>
       </c>
     </row>
@@ -3690,12 +3690,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15303</t>
+          <t>15329</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>33044</t>
+          <t>33190</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3705,12 +3705,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>23,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8934</t>
+          <t>8945</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21767</t>
+          <t>23110</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3740,12 +3740,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>30,2%</t>
+          <t>32,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>27946</t>
+          <t>28055</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>49641</t>
+          <t>51055</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3775,12 +3775,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>23,72%</t>
         </is>
       </c>
     </row>
@@ -3803,12 +3803,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12903</t>
+          <t>12659</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>32365</t>
+          <t>32019</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3818,12 +3818,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4785</t>
+          <t>4816</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15999</t>
+          <t>15454</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3853,12 +3853,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>20619</t>
+          <t>20658</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>41388</t>
+          <t>40785</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>18,95%</t>
         </is>
       </c>
     </row>
@@ -3916,12 +3916,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>20814</t>
+          <t>20310</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>40422</t>
+          <t>39908</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3931,12 +3931,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3951,12 +3951,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>11437</t>
+          <t>11729</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>25729</t>
+          <t>26486</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3966,12 +3966,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>35,69%</t>
+          <t>36,74%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3986,12 +3986,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>35387</t>
+          <t>35608</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>59948</t>
+          <t>59850</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>27,81%</t>
         </is>
       </c>
     </row>
@@ -4029,12 +4029,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>26847</t>
+          <t>26319</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>47719</t>
+          <t>47718</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4044,7 +4044,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -4064,12 +4064,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12930</t>
+          <t>13055</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27796</t>
+          <t>28261</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4079,12 +4079,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,56%</t>
+          <t>39,2%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4099,12 +4099,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>43299</t>
+          <t>43549</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>70295</t>
+          <t>70429</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4114,12 +4114,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>32,73%</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>23669</t>
+          <t>24133</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>44243</t>
+          <t>45130</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>31,53%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>5186</t>
+          <t>5230</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>17204</t>
+          <t>17577</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>32826</t>
+          <t>33088</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>55923</t>
+          <t>56699</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>26,35%</t>
         </is>
       </c>
     </row>
@@ -4372,12 +4372,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>91618</t>
+          <t>92498</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>133472</t>
+          <t>133375</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4387,12 +4387,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4407,12 +4407,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>74549</t>
+          <t>75314</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>110078</t>
+          <t>110741</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4422,12 +4422,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>177983</t>
+          <t>176588</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>234373</t>
+          <t>232602</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4457,12 +4457,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,74%</t>
         </is>
       </c>
     </row>
@@ -4485,12 +4485,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>133598</t>
+          <t>132684</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>178112</t>
+          <t>177903</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4500,12 +4500,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4520,12 +4520,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>108449</t>
+          <t>108306</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>148540</t>
+          <t>146947</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4535,12 +4535,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4555,12 +4555,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>254956</t>
+          <t>252540</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>314743</t>
+          <t>311418</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>19,74%</t>
         </is>
       </c>
     </row>
@@ -4598,12 +4598,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>216398</t>
+          <t>216820</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>272556</t>
+          <t>272584</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4613,7 +4613,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -4633,12 +4633,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>148002</t>
+          <t>149485</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>193259</t>
+          <t>191339</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>29,31%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>377362</t>
+          <t>378666</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>450181</t>
+          <t>454951</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>28,83%</t>
         </is>
       </c>
     </row>
@@ -4711,12 +4711,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>172228</t>
+          <t>174953</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>222894</t>
+          <t>224909</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4726,12 +4726,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4746,12 +4746,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>110601</t>
+          <t>109180</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>151737</t>
+          <t>150890</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4781,12 +4781,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>294816</t>
+          <t>290185</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>359319</t>
+          <t>359947</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>22,81%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>190453</t>
+          <t>188303</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>242031</t>
+          <t>243267</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>117161</t>
+          <t>115147</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>159712</t>
+          <t>158617</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>320138</t>
+          <t>315840</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>385829</t>
+          <t>385297</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>24,42%</t>
         </is>
       </c>
     </row>
@@ -5054,12 +5054,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>34019</t>
+          <t>33401</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>59800</t>
+          <t>59118</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5069,12 +5069,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5089,12 +5089,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>38500</t>
+          <t>38201</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>64142</t>
+          <t>63465</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5124,12 +5124,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>77599</t>
+          <t>77884</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>114453</t>
+          <t>116981</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,75%</t>
         </is>
       </c>
     </row>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>35915</t>
+          <t>35982</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>62921</t>
+          <t>62081</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5182,12 +5182,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5202,12 +5202,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>40097</t>
+          <t>40408</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>66611</t>
+          <t>66498</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5237,12 +5237,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>81579</t>
+          <t>83428</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>120765</t>
+          <t>121522</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,44%</t>
         </is>
       </c>
     </row>
@@ -5280,12 +5280,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>73192</t>
+          <t>71628</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>107189</t>
+          <t>106828</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5295,12 +5295,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>30,47%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5315,12 +5315,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>60842</t>
+          <t>61222</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>90132</t>
+          <t>89600</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5350,12 +5350,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>142940</t>
+          <t>143848</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>189019</t>
+          <t>187861</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5365,12 +5365,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>28,5%</t>
         </is>
       </c>
     </row>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>48985</t>
+          <t>49347</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>80191</t>
+          <t>81720</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5408,12 +5408,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5428,12 +5428,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>30408</t>
+          <t>30211</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>53888</t>
+          <t>53697</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>86210</t>
+          <t>85870</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>126609</t>
+          <t>124334</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>18,87%</t>
         </is>
       </c>
     </row>
@@ -5506,12 +5506,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>86354</t>
+          <t>88129</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>120910</t>
+          <t>121246</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5521,12 +5521,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>34,49%</t>
+          <t>34,58%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>74673</t>
+          <t>74735</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>106721</t>
+          <t>106280</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>34,6%</t>
+          <t>34,46%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>170465</t>
+          <t>170268</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>217718</t>
+          <t>218218</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>33,11%</t>
         </is>
       </c>
     </row>
@@ -5736,12 +5736,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>156841</t>
+          <t>155079</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>207350</t>
+          <t>205854</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5751,12 +5751,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5771,12 +5771,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>135195</t>
+          <t>134493</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>181116</t>
+          <t>177992</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>303396</t>
+          <t>305157</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>373921</t>
+          <t>372745</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,2%</t>
         </is>
       </c>
     </row>
@@ -5849,12 +5849,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>196837</t>
+          <t>196333</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>253026</t>
+          <t>252319</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5864,12 +5864,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5884,12 +5884,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>164684</t>
+          <t>163242</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>216219</t>
+          <t>217584</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>374730</t>
+          <t>374406</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>449772</t>
+          <t>450616</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,38%</t>
         </is>
       </c>
     </row>
@@ -5962,12 +5962,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>329071</t>
+          <t>329431</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>395486</t>
+          <t>396593</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5977,12 +5977,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5997,12 +5997,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>236126</t>
+          <t>234407</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>290636</t>
+          <t>288668</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6012,12 +6012,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>27,94%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6032,12 +6032,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>580631</t>
+          <t>584100</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>668792</t>
+          <t>666930</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6047,12 +6047,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>27,2%</t>
         </is>
       </c>
     </row>
@@ -6075,12 +6075,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>268488</t>
+          <t>265247</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>329547</t>
+          <t>330440</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6090,12 +6090,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6110,12 +6110,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>168092</t>
+          <t>165525</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>215947</t>
+          <t>218408</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6125,12 +6125,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>449026</t>
+          <t>449989</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>530055</t>
+          <t>528617</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6160,12 +6160,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>21,56%</t>
         </is>
       </c>
     </row>
@@ -6188,12 +6188,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>322563</t>
+          <t>319642</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>386359</t>
+          <t>386550</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6203,12 +6203,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>27,24%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6223,12 +6223,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>207760</t>
+          <t>210749</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>264228</t>
+          <t>264922</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6238,12 +6238,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>25,64%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>544049</t>
+          <t>544271</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>633436</t>
+          <t>636257</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6278,7 +6278,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>25,95%</t>
         </is>
       </c>
     </row>
